--- a/projects/Simoneau_Hendricks_1979/cases_summary.xlsx
+++ b/projects/Simoneau_Hendricks_1979/cases_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/roagr_dtu_dk/Documents/Roberto/Projects/Barotropic Model Validation/simoneau_hendricks_1979/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/roagr_dtu_dk/Documents/Roberto/Projects/barotropy/projects/Simoneau_Hendricks_1979/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_480197805B605F000F792611595ED87656CC3E0A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61EACAC2-5DC7-45A4-A276-E2D7610E74BF}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_480197805B605F000F792611595ED87656CC3E0A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D19DF3B-8BF5-49BD-A5F2-3C3FAA06C3C3}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -788,12 +788,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T114"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="7" max="7" width="10.06640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -855,7 +855,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A2">
         <v>1</v>
       </c>
@@ -917,7 +917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A3">
         <v>2</v>
       </c>
@@ -979,7 +979,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5381,7 +5381,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5877,7 +5877,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A94">
         <v>93</v>
       </c>
@@ -6621,7 +6621,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A97">
         <v>100</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A98">
         <v>101</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A99">
         <v>102</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A100">
         <v>103</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A101">
         <v>104</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A102">
         <v>105</v>
       </c>
@@ -7117,7 +7117,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A103">
         <v>106</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A104">
         <v>107</v>
       </c>
@@ -7241,7 +7241,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A105">
         <v>108</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A106">
         <v>109</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A107">
         <v>110</v>
       </c>
@@ -7427,7 +7427,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A108">
         <v>111</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A109">
         <v>112</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A110">
         <v>113</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A111">
         <v>114</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A112">
         <v>115</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.75">
       <c r="A113">
         <v>116</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:20" ht="14" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A114">
         <v>117</v>
       </c>

--- a/projects/Simoneau_Hendricks_1979/cases_summary.xlsx
+++ b/projects/Simoneau_Hendricks_1979/cases_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/roagr_dtu_dk/Documents/Roberto/Projects/barotropy/projects/Simoneau_Hendricks_1979/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/alber_dtu_dk/Documents/Documents/CFD/barotropy/projects/Simoneau_Hendricks_1979/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_480197805B605F000F792611595ED87656CC3E0A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D19DF3B-8BF5-49BD-A5F2-3C3FAA06C3C3}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_480197805B605F000F792611595ED87656CC3E0A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F671F03F-272D-46D7-AF1F-5D78751FEDD5}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -788,12 +788,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T114"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="7" max="7" width="10.04296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.07421875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -855,7 +855,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -917,7 +917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -979,7 +979,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5381,7 +5381,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5877,7 +5877,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>93</v>
       </c>
@@ -6621,7 +6621,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>100</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>101</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>102</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>103</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>104</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>105</v>
       </c>
@@ -7117,7 +7117,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>106</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>107</v>
       </c>
@@ -7241,7 +7241,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>108</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>109</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>110</v>
       </c>
@@ -7427,7 +7427,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A108">
         <v>111</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A109">
         <v>112</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A110">
         <v>113</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A111">
         <v>114</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A112">
         <v>115</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A113">
         <v>116</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="14" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A114">
         <v>117</v>
       </c>
@@ -7863,5 +7863,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>